--- a/ascend_test_suite/latest/SGLang_model_list.xlsx
+++ b/ascend_test_suite/latest/SGLang_model_list.xlsx
@@ -1,262 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ascend" sheetId="1" r:id="rId1"/>
+    <sheet name="Ascend" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
-  <si>
-    <t>模型名称</t>
-  </si>
-  <si>
-    <t>卡型</t>
-  </si>
-  <si>
-    <t>默认参数</t>
-  </si>
-  <si>
-    <t>注</t>
-  </si>
-  <si>
-    <t>DeepSeek-R1-Distill-Qwen-32B</t>
-  </si>
-  <si>
-    <t>H100</t>
-  </si>
-  <si>
-    <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 18432 --disable-radix-cache</t>
-  </si>
-  <si>
-    <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
-  </si>
-  <si>
-    <t>DeepSeek-R1-Distill-Llama-8B</t>
-  </si>
-  <si>
-    <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache</t>
-  </si>
-  <si>
-    <t>Qwen3-32B-FP8</t>
-  </si>
-  <si>
-    <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache</t>
-  </si>
-  <si>
-    <t>DeepSeek-R1-Distill-Llama-70B</t>
-  </si>
-  <si>
-    <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache</t>
-  </si>
-  <si>
-    <t>Qwen3-235B-A22B</t>
-  </si>
-  <si>
-    <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -571,163 +500,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -975,7 +904,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -984,7 +913,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -997,11 +926,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1253,169 +1245,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="33.1818181818182" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5.54545454545455" style="2" customWidth="1"/>
-    <col min="3" max="3" width="255.636363636364" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.6363636363636" style="2" customWidth="1"/>
+    <col width="33.1818181818182" customWidth="1" style="2" min="1" max="1"/>
+    <col width="5.54545454545455" customWidth="1" style="2" min="2" max="2"/>
+    <col width="255.636363636364" customWidth="1" style="2" min="3" max="3"/>
+    <col width="51.6363636363636" customWidth="1" style="2" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模型名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>卡型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>默认参数</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>注</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+      <c r="P1" s="3" t="n"/>
+      <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:20">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1-Distill-Qwen-32B</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 32768 --disable-radix-cache</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1-Distill-Llama-8B</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
     </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-32B-FP8</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
     </row>
-    <row r="5" spans="1:20">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1-Distill-Llama-70B</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
     </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-235B-A22B</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 18432 --disable-radix-cache" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0"/>
-    <hyperlink ref="C3" r:id="rId1" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0"/>
-    <hyperlink ref="C4" r:id="rId1" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0"/>
-    <hyperlink ref="C5" r:id="rId1" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0"/>
-    <hyperlink ref="C6" r:id="rId1" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 18432 --disable-radix-cache" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ascend_test_suite/latest/SGLang_model_list.xlsx
+++ b/ascend_test_suite/latest/SGLang_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 32768 --disable-radix-cache</t>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 32768 --disable-radix-cache --enable-metrics --enable-mfu-metrics</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache</t>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-8B --served-model-name DeepSeek-R1-Distill-Llama-8B --port 4321 --tp-size 1 --host 0.0.0.0 --disable-radix-cache --enable-metrics --enable-mfu-metrics</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache</t>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-32B-FP8 --served-model-name Qwen3-32B-FP8 --port 4321 --tp-size 2 --host 0.0.0.0 --disable-radix-cache --enable-metrics --enable-mfu-metrics</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache</t>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name DeepSeek-R1-Distill-Llama-70B --port 4321 --tp-size 4 --host 0.0.0.0 --disable-radix-cache --enable-metrics --enable-mfu-metrics</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache</t>
+          <t>docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name Qwen3-235B-A22B --port 4321 --tp-size 8 --host 0.0.0.0 --mem-fraction-static 0.98 --disable-radix-cache --enable-metrics --enable-mfu-metrics</t>
         </is>
       </c>
     </row>

--- a/ascend_test_suite/latest/SGLang_model_list.xlsx
+++ b/ascend_test_suite/latest/SGLang_model_list.xlsx
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="33.1818181818182" customWidth="1" style="2" min="1" max="1"/>
@@ -1446,6 +1446,28 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash-w8a8-mtp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>910B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>docker run -itd --name sglang_fl --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 setsid bash run_dsv4_v0516.sh --port 30010 --tp-size 8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SGLang Pagoda / sglang-universal-plugin；--tp-size 8 仅供 CI 解析卡数，实际并行度由 run_dsv4_v0516.sh 决定；需挂系统 customize OPP（含 MoeGatingTopKHash）；若 ImportError get_fused_compressor_rope_cos_sin 则设 SGLANG_DSV4_NPU_FUSED_COMPRESSOR=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run -it --name sglang_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; quay.io/ascend/sglang-ascend:v0.11.0 python3 -m sglang.launch_server --model-path /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name DeepSeek-R1-Distill-Qwen-32B --port 4321 --tp-size 2 --host 0.0.0.0 --context-length 18432 --disable-radix-cache" r:id="rId1"/>
